--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -12586,7 +12586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B670"/>
+  <dimension ref="A1:B671"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19289,6 +19289,16 @@
       </c>
       <c r="B670" t="n">
         <v>-0.71</v>
+      </c>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>2025-11-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B671" t="n">
+        <v>0.92</v>
       </c>
     </row>
   </sheetData>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E578"/>
+  <dimension ref="A1:E579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12572,6 +12572,27 @@
       <c r="E578" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="n">
+        <v>372.31</v>
+      </c>
+      <c r="C579" t="n">
+        <v>366.9</v>
+      </c>
+      <c r="D579" t="n">
+        <v>369.02</v>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12607,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B671"/>
+  <dimension ref="A1:B672"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19299,6 +19320,16 @@
       </c>
       <c r="B671" t="n">
         <v>0.92</v>
+      </c>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B672" t="n">
+        <v>1.46</v>
       </c>
     </row>
   </sheetData>
@@ -19467,28 +19498,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.008892049503046826</v>
+        <v>0.00787464155073243</v>
       </c>
       <c r="J2" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K2" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0005543042542472953</v>
+        <v>0.0004354548087196486</v>
       </c>
       <c r="M2" t="n">
-        <v>2.192014796172151</v>
+        <v>2.192633667636306</v>
       </c>
       <c r="N2" t="n">
-        <v>8.036049548553764</v>
+        <v>8.038364686926062</v>
       </c>
       <c r="O2" t="n">
-        <v>2.834792681758891</v>
+        <v>2.835200995860093</v>
       </c>
       <c r="P2" t="n">
-        <v>375.1501636352522</v>
+        <v>375.1605900151056</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19549,28 +19580,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06983341339114199</v>
+        <v>-0.06943659643041958</v>
       </c>
       <c r="J3" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K3" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05755800468031935</v>
+        <v>0.05710682524130029</v>
       </c>
       <c r="M3" t="n">
-        <v>1.661313220436776</v>
+        <v>1.66051273498094</v>
       </c>
       <c r="N3" t="n">
-        <v>4.500940925575383</v>
+        <v>4.495620986212256</v>
       </c>
       <c r="O3" t="n">
-        <v>2.121542110252677</v>
+        <v>2.120287948890965</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5390173046038</v>
+        <v>367.5349507309591</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19631,28 +19662,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07789139724905511</v>
+        <v>-0.07704861035666086</v>
       </c>
       <c r="J4" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="K4" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05726666117708823</v>
+        <v>0.05618909008491246</v>
       </c>
       <c r="M4" t="n">
-        <v>1.950263280517572</v>
+        <v>1.951485476314212</v>
       </c>
       <c r="N4" t="n">
-        <v>5.629811626444486</v>
+        <v>5.63120035264988</v>
       </c>
       <c r="O4" t="n">
-        <v>2.372722408214767</v>
+        <v>2.373015034223315</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5291243225909</v>
+        <v>368.5204874564689</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19694,7 +19725,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E578"/>
+  <dimension ref="A1:E579"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35303,6 +35334,33 @@
         </is>
       </c>
     </row>
+    <row r="579">
+      <c r="A579" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>-36.77079797917258,174.7731276010357</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>-36.77138164430947,174.77364637249855</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>-36.771940784654134,174.77420666862506</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E579"/>
+  <dimension ref="A1:E582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12591,6 +12591,69 @@
         <v>369.02</v>
       </c>
       <c r="E579" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="n">
+        <v>370.76</v>
+      </c>
+      <c r="C580" t="n">
+        <v>365.18</v>
+      </c>
+      <c r="D580" t="n">
+        <v>366.48</v>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="n">
+        <v>370.13</v>
+      </c>
+      <c r="C581" t="n">
+        <v>364.36</v>
+      </c>
+      <c r="D581" t="n">
+        <v>366.02</v>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="n">
+        <v>370.46</v>
+      </c>
+      <c r="C582" t="n">
+        <v>364.56</v>
+      </c>
+      <c r="D582" t="n">
+        <v>366.42</v>
+      </c>
+      <c r="E582" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12607,7 +12670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B672"/>
+  <dimension ref="A1:B675"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19330,6 +19393,36 @@
       </c>
       <c r="B672" t="n">
         <v>1.46</v>
+      </c>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B673" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B674" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B675" t="n">
+        <v>0.57</v>
       </c>
     </row>
   </sheetData>
@@ -19498,28 +19591,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00787464155073243</v>
+        <v>0.003031291872295602</v>
       </c>
       <c r="J2" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K2" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004354548087196486</v>
+        <v>6.425809201082711e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>2.192633667636306</v>
+        <v>2.202624221296538</v>
       </c>
       <c r="N2" t="n">
-        <v>8.038364686926062</v>
+        <v>8.120211346276836</v>
       </c>
       <c r="O2" t="n">
-        <v>2.835200995860093</v>
+        <v>2.849598453515308</v>
       </c>
       <c r="P2" t="n">
-        <v>375.1605900151056</v>
+        <v>375.2103760390091</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -19580,28 +19673,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.06943659643041958</v>
+        <v>-0.07042685061871104</v>
       </c>
       <c r="J3" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K3" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L3" t="n">
-        <v>0.05710682524130029</v>
+        <v>0.0591768145569761</v>
       </c>
       <c r="M3" t="n">
-        <v>1.66051273498094</v>
+        <v>1.657049156986268</v>
       </c>
       <c r="N3" t="n">
-        <v>4.495620986212256</v>
+        <v>4.478169422018486</v>
       </c>
       <c r="O3" t="n">
-        <v>2.120287948890965</v>
+        <v>2.116168571267064</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5349507309591</v>
+        <v>367.545131601519</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -19662,28 +19755,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07704861035666086</v>
+        <v>-0.07722749003105502</v>
       </c>
       <c r="J4" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="K4" t="n">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05618909008491246</v>
+        <v>0.05700819068086749</v>
       </c>
       <c r="M4" t="n">
-        <v>1.951485476314212</v>
+        <v>1.942291003437596</v>
       </c>
       <c r="N4" t="n">
-        <v>5.63120035264988</v>
+        <v>5.602502509230282</v>
       </c>
       <c r="O4" t="n">
-        <v>2.373015034223315</v>
+        <v>2.366960605762225</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5204874564689</v>
+        <v>368.5223262158779</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -19725,7 +19818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E579"/>
+  <dimension ref="A1:E582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35361,6 +35454,87 @@
         </is>
       </c>
     </row>
+    <row r="580">
+      <c r="A580" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:06:17+00:00</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>-36.77080643812531,174.77311378363854</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>-36.77139138527048,174.77363138482863</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>-36.77195483924212,174.77418421000914</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-31 22:12:25+00:00</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>-36.77080987627988,174.77310816753428</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>-36.77139602921638,174.7736242395428</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>-36.771957384560785,174.77418014269986</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>-36.77080807534181,174.77311110930322</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>-36.771394896546695,174.77362598229553</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>-36.771955171240215,174.77418367949056</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E582"/>
+  <dimension ref="A1:E583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12654,6 +12654,27 @@
         <v>366.42</v>
       </c>
       <c r="E582" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="n">
+        <v>368.4</v>
+      </c>
+      <c r="C583" t="n">
+        <v>362.59</v>
+      </c>
+      <c r="D583" t="n">
+        <v>365.73</v>
+      </c>
+      <c r="E583" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -12670,7 +12691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B675"/>
+  <dimension ref="A1:B676"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19423,6 +19444,16 @@
       </c>
       <c r="B675" t="n">
         <v>0.57</v>
+      </c>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B676" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -19591,34 +19622,30 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.003031291872295602</v>
+        <v>0.0007606056188193491</v>
       </c>
       <c r="J2" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K2" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L2" t="n">
-        <v>6.425809201082711e-05</v>
+        <v>4.020361335177469e-06</v>
       </c>
       <c r="M2" t="n">
-        <v>2.202624221296538</v>
+        <v>2.209179000617387</v>
       </c>
       <c r="N2" t="n">
-        <v>8.120211346276836</v>
+        <v>8.187320728482099</v>
       </c>
       <c r="O2" t="n">
-        <v>2.849598453515308</v>
+        <v>2.861349459342934</v>
       </c>
       <c r="P2" t="n">
-        <v>375.2103760390091</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>375.2338368342577</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.76980857416203 -36.77282977549785, 174.77801185853403 -36.76780764335105)</t>
@@ -19673,34 +19700,30 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07042685061871104</v>
+        <v>-0.07144747754655519</v>
       </c>
       <c r="J3" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K3" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0591768145569761</v>
+        <v>0.06079686280385466</v>
       </c>
       <c r="M3" t="n">
-        <v>1.657049156986268</v>
+        <v>1.659435819352693</v>
       </c>
       <c r="N3" t="n">
-        <v>4.478169422018486</v>
+        <v>4.48685200283361</v>
       </c>
       <c r="O3" t="n">
-        <v>2.116168571267064</v>
+        <v>2.118219063938763</v>
       </c>
       <c r="P3" t="n">
-        <v>367.545131601519</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>367.5556767480987</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.77044920683613 -36.77345948638678, 174.77846744481798 -36.76824805436688)</t>
@@ -19755,34 +19778,30 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07722749003105502</v>
+        <v>-0.07747556948574655</v>
       </c>
       <c r="J4" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="K4" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05700819068086749</v>
+        <v>0.05754023327919811</v>
       </c>
       <c r="M4" t="n">
-        <v>1.942291003437596</v>
+        <v>1.940162266484163</v>
       </c>
       <c r="N4" t="n">
-        <v>5.602502509230282</v>
+        <v>5.593843786932849</v>
       </c>
       <c r="O4" t="n">
-        <v>2.366960605762225</v>
+        <v>2.365130818143649</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5223262158779</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>368.5248893798919</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.77094371638117 -36.77398264139601, 174.7790801360495 -36.76889075339823)</t>
@@ -19818,7 +19837,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E582"/>
+  <dimension ref="A1:E583"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35535,6 +35554,33 @@
         </is>
       </c>
     </row>
+    <row r="583">
+      <c r="A583" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:06:02+00:00</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>-36.77081931756011,174.77309274553113</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>-36.77140605334211,174.77360881617898</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>-36.77195898921812,174.7741775785265</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E583"/>
+  <dimension ref="A1:E586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12677,6 +12677,69 @@
       <c r="E583" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="n">
+        <v>367.57</v>
+      </c>
+      <c r="C584" t="n">
+        <v>362.45</v>
+      </c>
+      <c r="D584" t="n">
+        <v>365.85</v>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>367.24</v>
+      </c>
+      <c r="C585" t="n">
+        <v>362.51</v>
+      </c>
+      <c r="D585" t="n">
+        <v>365.96</v>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>368.75</v>
+      </c>
+      <c r="C586" t="n">
+        <v>363.61</v>
+      </c>
+      <c r="D586" t="n">
+        <v>366.93</v>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12754,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B676"/>
+  <dimension ref="A1:B679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19454,6 +19517,36 @@
       </c>
       <c r="B676" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B677" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B678" t="n">
+        <v>-0.49</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B679" t="n">
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>
@@ -19622,28 +19715,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007606056188193491</v>
+        <v>-0.00649462224450122</v>
       </c>
       <c r="J2" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K2" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="L2" t="n">
-        <v>4.020361335177469e-06</v>
+        <v>0.0002864415935379672</v>
       </c>
       <c r="M2" t="n">
-        <v>2.209179000617387</v>
+        <v>2.231022306809824</v>
       </c>
       <c r="N2" t="n">
-        <v>8.187320728482099</v>
+        <v>8.423886757992861</v>
       </c>
       <c r="O2" t="n">
-        <v>2.861349459342934</v>
+        <v>2.902393281068722</v>
       </c>
       <c r="P2" t="n">
-        <v>375.2338368342577</v>
+        <v>375.309065765357</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19700,28 +19793,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07144747754655519</v>
+        <v>-0.0741965267876105</v>
       </c>
       <c r="J3" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K3" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06079686280385466</v>
+        <v>0.06535565925949693</v>
       </c>
       <c r="M3" t="n">
-        <v>1.659435819352693</v>
+        <v>1.665069371478527</v>
       </c>
       <c r="N3" t="n">
-        <v>4.48685200283361</v>
+        <v>4.505007936570374</v>
       </c>
       <c r="O3" t="n">
-        <v>2.118219063938763</v>
+        <v>2.122500397307471</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5556767480987</v>
+        <v>367.5841778960599</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19778,28 +19871,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07747556948574655</v>
+        <v>-0.0776898401710174</v>
       </c>
       <c r="J4" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="K4" t="n">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05754023327919811</v>
+        <v>0.05841974199161371</v>
       </c>
       <c r="M4" t="n">
-        <v>1.940162266484163</v>
+        <v>1.932854956875409</v>
       </c>
       <c r="N4" t="n">
-        <v>5.593843786932849</v>
+        <v>5.566617660675909</v>
       </c>
       <c r="O4" t="n">
-        <v>2.365130818143649</v>
+        <v>2.359368063841653</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5248893798919</v>
+        <v>368.5271060964581</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19837,7 +19930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E583"/>
+  <dimension ref="A1:E586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35581,6 +35674,87 @@
         </is>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>-36.770823847191,174.77308534653406</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>-36.77140684621072,174.7736075962517</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>-36.77195832522199,174.77417863956376</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-13 22:11:49+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-36.77082564812845,174.77308240476387</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-36.77140650640988,174.77360811907766</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-36.77195771655885,174.77417961218123</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-22 22:05:57+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-36.770817407474674,174.77309586558988</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-36.771400276727526,174.77361770421965</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-36.77195234925636,174.7741881888984</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E586"/>
+  <dimension ref="A1:E588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12740,6 +12740,48 @@
       <c r="E586" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>369.44</v>
+      </c>
+      <c r="C587" t="n">
+        <v>363.37</v>
+      </c>
+      <c r="D587" t="n">
+        <v>366.85</v>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>369.48</v>
+      </c>
+      <c r="C588" t="n">
+        <v>363.32</v>
+      </c>
+      <c r="D588" t="n">
+        <v>366.16</v>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -12754,7 +12796,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B679"/>
+  <dimension ref="A1:B681"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19547,6 +19589,26 @@
       </c>
       <c r="B679" t="n">
         <v>1.3</v>
+      </c>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B680" t="n">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B681" t="n">
+        <v>-0.7</v>
       </c>
     </row>
   </sheetData>
@@ -19715,28 +19777,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.00649462224450122</v>
+        <v>-0.01019159147459511</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K2" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0002864415935379672</v>
+        <v>0.0007010844854425935</v>
       </c>
       <c r="M2" t="n">
-        <v>2.231022306809824</v>
+        <v>2.240591672207382</v>
       </c>
       <c r="N2" t="n">
-        <v>8.423886757992861</v>
+        <v>8.503886395343216</v>
       </c>
       <c r="O2" t="n">
-        <v>2.902393281068722</v>
+        <v>2.916142382556657</v>
       </c>
       <c r="P2" t="n">
-        <v>375.309065765357</v>
+        <v>375.3475292582721</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19793,28 +19855,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0741965267876105</v>
+        <v>-0.07567231076862524</v>
       </c>
       <c r="J3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06535565925949693</v>
+        <v>0.06801512505696172</v>
       </c>
       <c r="M3" t="n">
-        <v>1.665069371478527</v>
+        <v>1.667054235266607</v>
       </c>
       <c r="N3" t="n">
-        <v>4.505007936570374</v>
+        <v>4.506981048900601</v>
       </c>
       <c r="O3" t="n">
-        <v>2.122500397307471</v>
+        <v>2.12296515489553</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5841778960599</v>
+        <v>367.5995322920378</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19871,28 +19933,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.0776898401710174</v>
+        <v>-0.07766026369665932</v>
       </c>
       <c r="J4" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K4" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05841974199161371</v>
+        <v>0.05877071487571861</v>
       </c>
       <c r="M4" t="n">
-        <v>1.932854956875409</v>
+        <v>1.927438708416324</v>
       </c>
       <c r="N4" t="n">
-        <v>5.566617660675909</v>
+        <v>5.548052423500006</v>
       </c>
       <c r="O4" t="n">
-        <v>2.359368063841653</v>
+        <v>2.355430411517183</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5271060964581</v>
+        <v>368.5268008359729</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19930,7 +19992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E586"/>
+  <dimension ref="A1:E588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35755,6 +35817,60 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-29 22:11:43+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-36.770813641877425,174.77310201656238</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-36.771401635931,174.77361561291607</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-36.77195279192051,174.7741874815403</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-15 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-36.77081342358192,174.7731023731405</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-36.771401919098395,174.7736151772278</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-36.771956609898595,174.77418138057664</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E588"/>
+  <dimension ref="A1:E594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12782,6 +12782,132 @@
       <c r="E588" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>370.59</v>
+      </c>
+      <c r="C589" t="n">
+        <v>363.84</v>
+      </c>
+      <c r="D589" t="n">
+        <v>366.44</v>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>370.8</v>
+      </c>
+      <c r="C590" t="n">
+        <v>364.08</v>
+      </c>
+      <c r="D590" t="n">
+        <v>366.01</v>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>370.57</v>
+      </c>
+      <c r="C591" t="n">
+        <v>364.25</v>
+      </c>
+      <c r="D591" t="n">
+        <v>365.67</v>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>372.42</v>
+      </c>
+      <c r="C592" t="n">
+        <v>364.19</v>
+      </c>
+      <c r="D592" t="n">
+        <v>363.46</v>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>372.68</v>
+      </c>
+      <c r="C593" t="n">
+        <v>364.33</v>
+      </c>
+      <c r="D593" t="n">
+        <v>363.77</v>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>373.23</v>
+      </c>
+      <c r="C594" t="n">
+        <v>364.48</v>
+      </c>
+      <c r="D594" t="n">
+        <v>364.31</v>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -12796,7 +12922,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B681"/>
+  <dimension ref="A1:B687"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19609,6 +19735,66 @@
       </c>
       <c r="B681" t="n">
         <v>-0.7</v>
+      </c>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B682" t="n">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B683" t="n">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B684" t="n">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B685" t="n">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B686" t="n">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B687" t="n">
+        <v>-0.87</v>
       </c>
     </row>
   </sheetData>
@@ -19777,28 +19963,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01019159147459511</v>
+        <v>-0.01659236984372935</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007010844854425935</v>
+        <v>0.001868914519347786</v>
       </c>
       <c r="M2" t="n">
-        <v>2.240591672207382</v>
+        <v>2.247996576600095</v>
       </c>
       <c r="N2" t="n">
-        <v>8.503886395343216</v>
+        <v>8.54037107873185</v>
       </c>
       <c r="O2" t="n">
-        <v>2.916142382556657</v>
+        <v>2.922391328814786</v>
       </c>
       <c r="P2" t="n">
-        <v>375.3475292582721</v>
+        <v>375.4143708988518</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -19855,28 +20041,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07567231076862524</v>
+        <v>-0.07831046209545102</v>
       </c>
       <c r="J3" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="K3" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06801512505696172</v>
+        <v>0.07364571161594347</v>
       </c>
       <c r="M3" t="n">
-        <v>1.667054235266607</v>
+        <v>1.663659204189989</v>
       </c>
       <c r="N3" t="n">
-        <v>4.506981048900601</v>
+        <v>4.480546464204084</v>
       </c>
       <c r="O3" t="n">
-        <v>2.12296515489553</v>
+        <v>2.116730134949679</v>
       </c>
       <c r="P3" t="n">
-        <v>367.5995322920378</v>
+        <v>367.6270878312528</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -19933,28 +20119,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.07766026369665932</v>
+        <v>-0.08054527052427779</v>
       </c>
       <c r="J4" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="K4" t="n">
-        <v>587</v>
+        <v>593</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05877071487571861</v>
+        <v>0.06382193196449448</v>
       </c>
       <c r="M4" t="n">
-        <v>1.927438708416324</v>
+        <v>1.921995598592056</v>
       </c>
       <c r="N4" t="n">
-        <v>5.548052423500006</v>
+        <v>5.527520522523546</v>
       </c>
       <c r="O4" t="n">
-        <v>2.355430411517183</v>
+        <v>2.351067953616727</v>
       </c>
       <c r="P4" t="n">
-        <v>368.5268008359729</v>
+        <v>368.556968241492</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -19992,7 +20178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E588"/>
+  <dimension ref="A1:E594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -35871,6 +36057,168 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-36.77080736588134,174.77311226818188</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-36.77139897415747,174.7736197083855</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-36.771955060574186,174.7741838563301</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-36.77080621982979,174.77311414021656</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-36.77139761495391,174.7736217996889</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-36.7719574398938,174.7741800542801</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-08 22:11:04+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-36.7708074750291,174.77311208989286</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-36.7713966521847,174.7736232810288</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-36.77195932121619,174.77417704800786</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:37+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-36.77079737885975,174.77312858162506</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-36.7713969919856,174.77362275820295</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-36.771971549809976,174.77415750723458</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-36.77079595993847,174.7731308993817</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-36.771396199116836,174.7736239781299</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-36.771969834487045,174.7741602482484</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-36.77079295837409,174.77313580232808</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-36.771395349614565,174.77362528519444</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-36.77196684650502,174.77416502291734</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0169/nzd0169.xlsx
+++ b/data/nzd0169/nzd0169.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E594"/>
+  <dimension ref="A1:E597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12906,6 +12906,69 @@
         <v>364.31</v>
       </c>
       <c r="E594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>372.49</v>
+      </c>
+      <c r="C595" t="n">
+        <v>364.54</v>
+      </c>
+      <c r="D595" t="n">
+        <v>364.39</v>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>372.76</v>
+      </c>
+      <c r="C596" t="n">
+        <v>364.75</v>
+      </c>
+      <c r="D596" t="n">
+        <v>364.98</v>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>373.77</v>
+      </c>
+      <c r="C597" t="n">
+        <v>365.74</v>
+      </c>
+      <c r="D597" t="n">
+        <v>367.01</v>
+      </c>
+      <c r="E597" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -12922,7 +12985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B687"/>
+  <dimension ref="A1:B691"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19795,6 +19858,46 @@
       </c>
       <c r="B687" t="n">
         <v>-0.87</v>
+      </c>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B688" t="n">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B689" t="n">
+        <v>-0.91</v>
+      </c>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B690" t="n">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B691" t="n">
+        <v>-0.9</v>
       </c>
     </row>
   </sheetData>
@@ -19963,28 +20066,28 @@
         <v>0.07049999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01659236984372935</v>
+        <v>-0.01845431048539821</v>
       </c>
       <c r="J2" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K2" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001868914519347786</v>
+        <v>0.002329634248521284</v>
       </c>
       <c r="M2" t="n">
-        <v>2.247996576600095</v>
+        <v>2.245558808483953</v>
       </c>
       <c r="N2" t="n">
-        <v>8.54037107873185</v>
+        <v>8.518046176648372</v>
       </c>
       <c r="O2" t="n">
-        <v>2.922391328814786</v>
+        <v>2.918569200250077</v>
       </c>
       <c r="P2" t="n">
-        <v>375.4143708988518</v>
+        <v>375.433906202712</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -20041,28 +20144,28 @@
         <v>0.096</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.07831046209545102</v>
+        <v>-0.07879779676199966</v>
       </c>
       <c r="J3" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K3" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.07364571161594347</v>
+        <v>0.07518403216089897</v>
       </c>
       <c r="M3" t="n">
-        <v>1.663659204189989</v>
+        <v>1.658521846192087</v>
       </c>
       <c r="N3" t="n">
-        <v>4.480546464204084</v>
+        <v>4.460698488011341</v>
       </c>
       <c r="O3" t="n">
-        <v>2.116730134949679</v>
+        <v>2.112036573549649</v>
       </c>
       <c r="P3" t="n">
-        <v>367.6270878312528</v>
+        <v>367.6321971948114</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -20119,28 +20222,28 @@
         <v>0.0915</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.08054527052427779</v>
+        <v>-0.08143298724520188</v>
       </c>
       <c r="J4" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="K4" t="n">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L4" t="n">
-        <v>0.06382193196449448</v>
+        <v>0.06566902760784055</v>
       </c>
       <c r="M4" t="n">
-        <v>1.921995598592056</v>
+        <v>1.918804774314182</v>
       </c>
       <c r="N4" t="n">
-        <v>5.527520522523546</v>
+        <v>5.510435291749848</v>
       </c>
       <c r="O4" t="n">
-        <v>2.351067953616727</v>
+        <v>2.347431637289966</v>
       </c>
       <c r="P4" t="n">
-        <v>368.556968241492</v>
+        <v>368.5662737760064</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -20178,7 +20281,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E594"/>
+  <dimension ref="A1:E597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36219,6 +36322,87 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-09 22:10:54+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-36.77079699684248,174.77312920563648</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-36.77139500981366,174.77362580802026</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-36.77196640384102,174.77416573027566</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-36.770795523347296,174.77313161253753</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-36.77139382051047,174.77362763791058</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-36.77196313919375,174.7741709470431</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-36.77079001138343,174.77314061612958</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-36.771388213795014,174.77363626453553</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-36.771951906592214,174.77418889625645</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
